--- a/artfynd/A 38105-2025 artfynd.xlsx
+++ b/artfynd/A 38105-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111220064</v>
+        <v>111220062</v>
       </c>
       <c r="B2" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>522215.1652588727</v>
+        <v>522230</v>
       </c>
       <c r="R2" t="n">
-        <v>6902887.646513243</v>
+        <v>6902832</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2023-08-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-08-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,15 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111220068</v>
+        <v>111220064</v>
       </c>
       <c r="B3" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -849,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522113.4111237399</v>
+        <v>522215</v>
       </c>
       <c r="R3" t="n">
-        <v>6902894.429735499</v>
+        <v>6902888</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,19 +862,9 @@
           <t>2023-08-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-08-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -940,12 +910,7 @@
         <v>111220066</v>
       </c>
       <c r="B4" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -980,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522197.6952060939</v>
+        <v>522198</v>
       </c>
       <c r="R4" t="n">
-        <v>6902848.397218144</v>
+        <v>6902848</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,19 +978,9 @@
           <t>2023-08-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-08-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1068,6 +1023,340 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>111220067</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Flomyrbäcken, Ramsjö, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>522185</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6902844</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Johan Myhrer</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Johan Myhrer</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>111220068</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Flomyrbäcken, Ramsjö, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>522113</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6902894</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johan Myhrer</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Johan Myhrer</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>111220060</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Flomyrbäcken, Ramsjö, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>522279</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6902821</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Johan Myhrer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Johan Myhrer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38105-2025 artfynd.xlsx
+++ b/artfynd/A 38105-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111220062</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111220064</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111220066</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1139,6 +1159,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111220067</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1255,6 +1280,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111220068</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1357,8 +1387,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111220060</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>